--- a/data/trans_bre/P05A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P05A_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 4,51</t>
+          <t>-8,12; 5,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 9,57</t>
+          <t>-7,44; 10,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 21,37</t>
+          <t>3,21; 20,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 3,24</t>
+          <t>-2,46; 3,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,32; 30,52</t>
+          <t>-38,58; 33,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 24,32</t>
+          <t>-15,92; 25,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,2; 67,86</t>
+          <t>7,82; 63,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-56,24; 204,6</t>
+          <t>-47,5; 158,61</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-8,31%</t>
+          <t>-7,34%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 9,28</t>
+          <t>-3,07; 8,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 9,14</t>
+          <t>-3,52; 9,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 3,67</t>
+          <t>-8,73; 3,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 3,48</t>
+          <t>-6,42; 3,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 30,77</t>
+          <t>-8,51; 29,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 25,8</t>
+          <t>-8,33; 26,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 6,95</t>
+          <t>-15,34; 7,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,48; 31,96</t>
+          <t>-35,09; 31,79</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,24</t>
+          <t>-1,91</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-9,41%</t>
+          <t>-8,05%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,72; 24,64</t>
+          <t>9,95; 23,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 15,4</t>
+          <t>-1,34; 15,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 4,55</t>
+          <t>-10,18; 4,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 3,45</t>
+          <t>-8,06; 3,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,11; 131,55</t>
+          <t>37,23; 127,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 37,87</t>
+          <t>-2,49; 37,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 16,82</t>
+          <t>-29,12; 15,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-30,13; 17,0</t>
+          <t>-29,83; 19,89</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,2</t>
+          <t>2,12</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-20,29%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 1,94</t>
+          <t>-11,58; 1,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 15,3</t>
+          <t>1,59; 15,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 11,28</t>
+          <t>-2,37; 11,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 3,38</t>
+          <t>-4,23; 8,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 7,82</t>
+          <t>-35,34; 6,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 51,57</t>
+          <t>4,52; 52,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 41,25</t>
+          <t>-6,95; 43,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,24; 18,2</t>
+          <t>-18,79; 56,76</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,71</t>
+          <t>-3,85</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-57,16%</t>
+          <t>-65,47%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 7,42</t>
+          <t>-12,77; 6,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 2,85</t>
+          <t>-16,93; 1,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 9,14</t>
+          <t>-6,7; 9,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 0,4</t>
+          <t>-7,98; -0,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 17,6</t>
+          <t>-24,97; 15,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 4,13</t>
+          <t>-22,55; 1,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,17; 48,52</t>
+          <t>-25,12; 49,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-85,85; 38,75</t>
+          <t>-86,69; -22,36</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>2,11</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,7; 18,61</t>
+          <t>4,11; 18,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 0,44</t>
+          <t>-16,76; 0,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 1,47</t>
+          <t>-15,75; 1,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 7,41</t>
+          <t>-3,32; 7,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,78; 133,72</t>
+          <t>19,64; 135,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-31,08; 0,88</t>
+          <t>-30,28; 2,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,07; 4,09</t>
+          <t>-35,59; 2,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 45,59</t>
+          <t>-15,84; 49,35</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18,83</t>
+          <t>2,85</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,1; 14,35</t>
+          <t>4,13; 14,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 3,17</t>
+          <t>-7,44; 3,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 7,13</t>
+          <t>-3,86; 7,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 45,17</t>
+          <t>-2,21; 8,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,98; 68,02</t>
+          <t>15,87; 70,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 8,19</t>
+          <t>-16,78; 9,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 19,93</t>
+          <t>-9,26; 19,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,04; 159,42</t>
+          <t>-6,38; 27,78</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,08</t>
+          <t>5,59</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 8,29</t>
+          <t>-1,88; 8,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 3,01</t>
+          <t>-5,97; 2,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 4,01</t>
+          <t>-4,89; 4,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,99; 16,21</t>
+          <t>1,64; 9,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 22,33</t>
+          <t>-4,42; 22,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,14; 13,59</t>
+          <t>-21,45; 12,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 15,73</t>
+          <t>-16,11; 15,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>25,32; 305,42</t>
+          <t>9,11; 68,66</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,39</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,11</t>
+          <t>2,5; 6,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,67</t>
+          <t>-2,15; 2,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,93</t>
+          <t>-1,76; 2,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,94; 21,95</t>
+          <t>-0,28; 3,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,4; 25,16</t>
+          <t>8,29; 24,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 7,02</t>
+          <t>-5,26; 6,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 8,31</t>
+          <t>-4,78; 8,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,79; 129,75</t>
+          <t>-1,47; 20,26</t>
         </is>
       </c>
     </row>
